--- a/ig/mc-changes-1.0.1/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:27:05+00:00</t>
+    <t>2023-06-08T09:38:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-changes-1.0.1/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:38:17+00:00</t>
+    <t>2023-06-08T10:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
